--- a/02_加值成品/生物/生物1-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物1-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物1-3 生物體的組成層次　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物1-3 生物體的組成層次　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>生物體組成由小到大順序？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>組織專職、器官整合、系統協同完成功能</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>單細胞能自行完成所有生命活動</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>有,如根由多種組織構成器官</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>細胞組織器官系統個體</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>層次</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>功能相似細胞的集合是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>單細胞</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>最高層</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>組織</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>集合</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>不同組織組成的是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>單細胞</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>單細胞生物</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>最高層</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>器官</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>器官</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>器官協同組成的是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>系統</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>單細胞</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>器官</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>系統</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>只由一個細胞組成的生物是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>系統</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>單細胞</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>單細胞生物</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>分工合作</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>單一</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>心臟屬於哪個層次？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>組織</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>器官</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>單細胞生物</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>器官</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>多細胞生物細胞會？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>組織</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>單細胞生物</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>分工合作</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>器官</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>協作</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>組織的下一層次是？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>組織</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>系統</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>單細胞生物</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>器官</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>向上</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>胃屬於哪個組成層次？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>器官</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>分工合作</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>最高層</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>單細胞</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>器官</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>血液屬於哪個組成層次？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>分工合作</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>組織</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>器官</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>單細胞</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>結締組織</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物1-3 生物體的組成層次　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物1-3 生物體的組成層次　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>變形蟲屬單細胞還多細胞？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>單細胞</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>多個器官</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>相似功能細胞</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>單細胞生物</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>一個細胞</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>消化系統由什麼組成？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>組織</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>器官</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>多個器官</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>分工合作</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>器官協同</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>肌肉組織屬哪個層次？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>器官</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>單細胞</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>組織</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>單細胞生物</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>層次</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>單細胞生物有器官嗎？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>沒有</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>最高層</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>系統</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>多個器官</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>一個細胞</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>組織是由什麼組成？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>相似功能細胞</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>器官</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>組織</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>最高層</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>細胞</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>個體是層次中的？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>器官</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>組織</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>分工合作</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>最高層</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>完整</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>植物的保護組織屬？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>單細胞生物</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>組織</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>分工合作</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>層次</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>系統的下一層是？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>器官</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>組織</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>單細胞</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>向下</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>神經細胞集合成什麼層次？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>組織</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>最高層</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>系統</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>單細胞生物</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>組織</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>植物的根屬於哪個層次？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>器官</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>分工合作</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>最高層</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>系統</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>器官</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物1-3 生物體的組成層次　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物1-3 生物體的組成層次　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>說明從細胞到個體的組成層次與意義？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>組織專職、器官整合、系統協同完成功能</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>單細胞簡便、多細胞分工可複雜化</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>有,如根由多種組織構成器官</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>逐層分工協作使複雜生命活動有效進行</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>層次</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何單細胞生物雖只有一細胞卻完整？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>提高效率與適應複雜環境</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>由多種組織構成的器官</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>多種組織構成器官</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>單細胞能自行完成所有生命活動</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>完整</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>組織器官系統如何分工合作？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>單細胞能自行完成所有生命活動</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>單細胞簡便、多細胞分工可複雜化</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>組織專職、器官整合、系統協同完成功能</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>細胞組織器官系統個體</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>分工</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>比較單細胞與多細胞生物優勢？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>多種組織構成器官</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>提高效率與適應複雜環境</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>逐層分工協作使複雜生命活動有效進行</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>單細胞簡便、多細胞分工可複雜化</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>比較</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>以消化為例說明系統層次？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>口胃腸等器官組成消化系統協同消化</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>由多種組織構成的器官</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>組織專職、器官整合、系統協同完成功能</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>單細胞能自行完成所有生命活動</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>實例</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>組織與器官的關係？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>多種組織構成器官</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>提高效率與適應複雜環境</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>逐層分工協作使複雜生命活動有效進行</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>單細胞能自行完成所有生命活動</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>關係</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>層次分明對生物體有何好處？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>有,如根由多種組織構成器官</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>單細胞能自行完成所有生命活動</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>提高效率與適應複雜環境</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>多種組織構成器官</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>好處</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>植物也有組成層次嗎?舉例</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>有,如根由多種組織構成器官</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>細胞組織器官系統個體</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>口胃腸等器官組成消化系統協同消化</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>單細胞簡便、多細胞分工可複雜化</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>植物</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>以植物根為例說明其組成層次？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>由多種組織構成的器官</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>細胞組織器官系統個體</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>單細胞簡便、多細胞分工可複雜化</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>多種組織構成器官</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>植物</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>為何多細胞生物需要組織分工？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>逐層分工協作使複雜生命活動有效進行</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>細胞組織器官系統個體</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>提升效率執行複雜功能</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>組織專職、器官整合、系統協同完成功能</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>分工</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物1-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物1-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>層次</t>
+          <t>由簡到繁：多細胞生物的組成順序是細胞、組織、器官、系統，最後組成個體</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>集合</t>
+          <t>細胞集合：許多功能相似的細胞聚在一起，共同完成某項工作，就稱為組織</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>器官</t>
+          <t>組織組成：由好幾種不同的組織一起組成，能執行特定功能的構造叫做器官</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>系統</t>
+          <t>器官協同：好幾個器官互相合作，共同完成某項生理功能，就組成系統</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>單一</t>
+          <t>一個細胞：像變形蟲這樣整個身體只有一個細胞的生物，稱為單細胞生物</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>器官</t>
+          <t>屬於器官：心臟由肌肉等多種組織組成，能執行打出血液的功能，是器官</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>協作</t>
+          <t>分工合作：多細胞生物體內的細胞會各自負責不同工作，互相配合完成生命活動</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>向上</t>
+          <t>往上一層：組成層次由小到大排列時，組織的上一層就是器官</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>器官</t>
+          <t>器官：胃是由多種組織組合而成、能執行消化功能的構造，屬於器官這個層次</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>結締組織</t>
+          <t>結締組織：血液是由許多相同或相似的細胞（血球）加上血漿構成，共同執行運輸功能，屬於結締組織</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>一個細胞</t>
+          <t>單一細胞：變形蟲整個身體只由一個細胞構成，能獨自完成所有生命活動</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>器官協同</t>
+          <t>多器官組成：消化系統是由口、胃、小腸等多個器官協同合作組成的</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>層次</t>
+          <t>屬於組織：肌肉組織是由許多功能相似的肌肉細胞聚集而成，屬於組織層次</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>一個細胞</t>
+          <t>沒有器官：單細胞生物全身只有一個細胞，不會再分出組織或器官</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>細胞</t>
+          <t>相似細胞組成：許多功能相似的細胞聚集在一起，就形成了組織</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>完整</t>
+          <t>最高層次：個體是由各系統整合而成的完整生物體，是組成層次中最高的一層</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>層次</t>
+          <t>屬於組織：保護組織是植物體表由相似細胞構成的一層構造，屬於組織層次</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>向下</t>
+          <t>往下一層：組成層次由大到小排列時，系統的下一層就是器官</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>組織</t>
+          <t>組織：許多構造和功能相似的神經細胞聚集在一起，就形成神經組織，負責傳遞訊息</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>器官</t>
+          <t>器官：根是由多種組織（如表皮、輸導組織等）組合而成、負責吸收水分養分的構造，屬於器官</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>層次</t>
+          <t>逐層分工：從細胞到個體一層層分工合作，能讓複雜的生命活動更有效率地進行</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>完整</t>
+          <t>獨立完整：單細胞生物雖然只有一個細胞，但這個細胞能獨自完成營養、呼吸等所有生命活動</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>分工</t>
+          <t>層層合作：組織各自專精工作，器官整合多種組織，系統再讓多個器官協同運作</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>比較</t>
+          <t>各有優勢：單細胞生物構造簡單容易存活，多細胞生物能分工合作發展出複雜功能</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>實例</t>
+          <t>實例說明：口、胃、腸等多個器官一起合作，共同組成負責消化食物的消化系統</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>關係</t>
+          <t>組成關係：好幾種不同的組織組合在一起，才能構成一個能執行功能的器官</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>好處</t>
+          <t>提升效率：組成層次分明能讓身體分工更精細，提高運作效率並適應複雜環境</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>植物</t>
+          <t>植物也有：植物的根同樣是由多種組織組合而成的器官，具有相同的組成層次</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>植物</t>
+          <t>植物：根本身是器官，由表皮組織、輸導組織等多種組織組合而成，這些組織又是由許多細胞構成，層層組合形成完整的根</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>分工</t>
+          <t>分工：不同組織各自負責特定的工作，彼此分工合作，能讓生物體更有效率地完成複雜的生理功能，比單一細胞獨自運作更有效</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/生物/生物1-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物1-3_三種難度測驗卷.xlsx
@@ -643,17 +643,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>單細胞</t>
+          <t>系統</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>單細胞生物</t>
+          <t>相似功能細胞</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>最高層</t>
+          <t>組織</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>單細胞</t>
+          <t>最高層</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>組織</t>
+          <t>系統</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>沒有</t>
+          <t>分工合作</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -843,17 +843,17 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>組織</t>
+          <t>系統</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>系統</t>
+          <t>最高層</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>單細胞生物</t>
+          <t>沒有</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>分工合作</t>
+          <t>相似功能細胞</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>最高層</t>
+          <t>組織</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>單細胞</t>
+          <t>單細胞生物</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1044,17 +1044,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>組織</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>系統</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
           <t>多個器官</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>相似功能細胞</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>單細胞生物</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>組織</t>
+          <t>單細胞生物</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>器官</t>
+          <t>相似功能細胞</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>分工合作</t>
+          <t>單細胞</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1324,12 +1324,12 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>分工合作</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
           <t>組織</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>沒有</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1404,17 +1404,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>分工合作</t>
+          <t>系統</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>最高層</t>
+          <t>相似功能細胞</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>系統</t>
+          <t>單細胞生物</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>逐層分工協作使複雜生命活動有效進行</t>
+          <t>提升效率執行複雜功能</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>單細胞能自行完成所有生命活動</t>
+          <t>口胃腸等器官組成消化系統協同消化</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1800,17 +1800,17 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>細胞組織器官系統個體</t>
+          <t>口胃腸等器官組成消化系統協同消化</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>口胃腸等器官組成消化系統協同消化</t>
+          <t>提升效率執行複雜功能</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>單細胞簡便、多細胞分工可複雜化</t>
+          <t>逐層分工協作使複雜生命活動有效進行</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
